--- a/División/MDC_División.xlsx
+++ b/División/MDC_División.xlsx
@@ -428,16 +428,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="2">
-        <v>42.22300000000001</v>
+        <v>42.223</v>
       </c>
       <c r="C2" s="2">
-        <v>115.6843833269236</v>
+        <v>115.6843833269237</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2">
-        <v>48.84541717212697</v>
+        <v>48.84541717212699</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -471,7 +471,7 @@
         <v>6</v>
       </c>
       <c r="E4" s="2">
-        <v>21.51425884562248</v>
+        <v>21.51425884562249</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -479,7 +479,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="2">
-        <v>23.68700000000001</v>
+        <v>23.687</v>
       </c>
       <c r="C5" s="2">
         <v>112.7845110465006</v>
